--- a/handoff/한화손보_장기CM_태깅가이드.xlsx
+++ b/handoff/한화손보_장기CM_태깅가이드.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카피안" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'태깅가이드'!$A$1:$J$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'태깅가이드'!$A$1:$J$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1077,6 +1077,47 @@
         <v>63</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>해외장기체류보험</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1088,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3619,8 +3660,261 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>해외장기체류보험</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="해외체류 중 질병이나 상해를 입어 해외의료기관에서 치료를 받은 경우 최대 10만달러까지 보장해…"&gt;</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="3개월 초과 해외체류·유학 중 질병·상해 의료비를 최대 10만달러까지. 한화손보 캐롯 해외장기체류보험을 온라인에서 확인하세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>70자</t>
+        </is>
+      </c>
+      <c r="J51" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>해외장기체류보험</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>분기(carrotBridge) 색인·canonical 정리</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- /cmcom/carrotBridge.do?carrot=overseas-long : 302(추정) 이동·canonical 없음·campaignId 중복 --&gt;</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- 목적지가 정본이면 301 + canonical 통일 --&gt;
+&lt;link rel="canonical" href="https://www.carrotins.com/product/overseas-long/intro"&gt;
+&lt;!-- 또는 CM이 랭킹 확보시 hanwhadirect에 상품 콘텐츠 랜딩 신설 --&gt;</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr"/>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>해외장기체류보험</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>&lt;title&gt; 교체</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보 캐롯 해외장기체류보험 | 3개월 초과 여행, 장기 유학시 보장&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보 캐롯 해외장기체류보험 | 유학·장기체류 보장&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>29자</t>
+        </is>
+      </c>
+      <c r="J53" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>해외장기체류보험</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>OG 태그 세트 추가/점검</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta property="og:title" content="유학·장기출장 전 필수 — 한화손보 캐롯 해외장기체류보험"&gt;
+&lt;meta property="og:description" content="3개월 넘는 해외체류, 현지 의료비까지 대비하는 장기체류보험. 개인정보 없이 보험료를 확인해요."&gt;
+&lt;meta property="og:image" content="https://.../og/overseaslong_1200x630.png"&gt;
+&lt;meta property="og:url" content="https://www.carrotins.com/product/overseas-long/intro"&gt;</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr"/>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>해외장기체류보험</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>상품 이미지 alt 텍스트 보강</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/overseaslong_cover.png"&gt;</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/overseaslong_cover.png" alt="해외장기체류보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr"/>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J50"/>
+  <autoFilter ref="A1:J55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3631,7 +3925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3977,6 +4271,39 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>해외장기체류보험</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯 해외장기체류보험 | 유학·장기체류 보장</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>3개월 초과 해외체류·유학 중 질병·상해 의료비를 최대 10만달러까지. 한화손보 캐롯 해외장기체류보험을 온라인에서 확인하세요.</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>유학·장기출장 전 필수 — 한화손보 캐롯 해외장기체류보험</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>3개월 넘는 해외체류, 현지 의료비까지 대비하는 장기체류보험. 개인정보 없이 보험료를 확인해요.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/handoff/한화손보_장기CM_태깅가이드.xlsx
+++ b/handoff/한화손보_장기CM_태깅가이드.xlsx
@@ -1321,22 +1321,77 @@
           <t>https://m.hanwhadirect.com/</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>robots.txt · sitemap.xml 설치/점검 (사이트 전체)</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t># https://www.hanwhadirect.com/robots.txt → 현재 403 (설치·크롤러 허용 여부 확인 필요)</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t># robots.txt (사이트 루트)
+User-agent: Yeti
+Allow: /
+User-agent: Googlebot
+Allow: /
+User-agent: *
+Allow: /
+Sitemap: https://www.hanwhadirect.com/sitemap.xml</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr"/>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>다이렉트 홈(메인)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>메인</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="한화손보다이렉트 — 필요한 보험을 한 곳에서"&gt;
 &lt;meta property="og:description" content="장기보험을 개인정보 없이 3분 만에 비교하고 보험료를 확인해요."&gt;
@@ -1344,101 +1399,53 @@
 &lt;meta property="og:url" content="https://m.hanwhadirect.com/"&gt;</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr"/>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr"/>
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>다이렉트 홈(메인)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>메인</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>모바일(m.)·PC(www) 메타 일치 + canonical</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- m./www 메타 상이·canonical 누락 가능 --&gt;</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>&lt;link rel="canonical" href="https://www.hanwhadirect.com/"&gt;
 &lt;link rel="alternate" media="only screen and (max-width: 640px)" href="https://m.hanwhadirect.com/"&gt;</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>다이렉트 홈(메인)</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>메인</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>사이트명·브랜드 구조화(WebSite/Organization)</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- WebSite/Organization 구조화 없음 --&gt;</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>&lt;script type="application/ld+json"&gt;{"@context":"https://schema.org","@type":"WebSite","name":"한화손해보험 다이렉트","url":"https://www.hanwhadirect.com/"}&lt;/script&gt;</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr"/>

--- a/handoff/한화손보_장기CM_태깅가이드.xlsx
+++ b/handoff/한화손보_장기CM_태깅가이드.xlsx
@@ -1345,6 +1345,14 @@
 Allow: /
 User-agent: *
 Allow: /
+Disallow: /cmcom/
+Disallow: /admin/
+Disallow: /manager/
+Disallow: /mng/
+Disallow: /search
+Disallow: /*?keyword=
+Disallow: /*?q=
+Sitemap: https://m.hanwhadirect.com/sitemap.xml
 Sitemap: https://www.hanwhadirect.com/sitemap.xml</t>
         </is>
       </c>

--- a/handoff/한화손보_장기CM_태깅가이드.xlsx
+++ b/handoff/한화손보_장기CM_태깅가이드.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카피안" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'태깅가이드'!$A$1:$J$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'태깅가이드'!$A$1:$J$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1328,15 +1328,63 @@
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
+          <t>검색로봇(Yeti) 접근 차단 해제 (방화벽/서버)</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t># Yeti 접근 시 HTTP 403 (방화벽/WAF 차단 의심) UA: Mozilla/5.0 (compatible; Yeti/1.1; +http://naver.me/spd)</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t># 방화벽/WAF·서버에서 Yeti·Googlebot·Daumoa UA 허용 → 정상 200 응답</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr"/>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>다이렉트 홈(메인)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>메인</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
           <t>robots.txt · sitemap.xml 설치/점검 (사이트 전체)</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t># https://www.hanwhadirect.com/robots.txt → 현재 403 (설치·크롤러 허용 여부 확인 필요)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t># robots.txt (사이트 루트)
 User-agent: Yeti
@@ -1356,50 +1404,50 @@
 Sitemap: https://www.hanwhadirect.com/sitemap.xml</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr"/>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr"/>
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>다이렉트 홈(메인)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>메인</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="한화손보다이렉트 — 필요한 보험을 한 곳에서"&gt;
 &lt;meta property="og:description" content="장기보험을 개인정보 없이 3분 만에 비교하고 보험료를 확인해요."&gt;
@@ -1407,103 +1455,55 @@
 &lt;meta property="og:url" content="https://m.hanwhadirect.com/"&gt;</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr"/>
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>다이렉트 홈(메인)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>메인</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>모바일(m.)·PC(www) 메타 일치 + canonical</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- m./www 메타 상이·canonical 누락 가능 --&gt;</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>&lt;link rel="canonical" href="https://www.hanwhadirect.com/"&gt;
 &lt;link rel="alternate" media="only screen and (max-width: 640px)" href="https://m.hanwhadirect.com/"&gt;</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr"/>
-      <c r="J6" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>다이렉트 홈(메인)</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>메인</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/home_cover.png"&gt;</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/home_cover.png" alt="다이렉트 홈(메인) 보장내용 안내"&gt;</t>
-        </is>
-      </c>
       <c r="I7" s="12" t="inlineStr"/>
       <c r="J7" s="12" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>주택화재보험</t>
+          <t>다이렉트 홈(메인)</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
@@ -1524,39 +1524,35 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>한화손보다이렉트 직접</t>
+          <t>메인</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
+          <t>https://m.hanwhadirect.com/</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>&lt;title&gt; 교체</t>
+          <t>로봇 메타태그 noindex 점검</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;화재&gt;고객정보입력&lt;/title&gt;</t>
+          <t>&lt;meta name="robots" content="noindex"&gt;  (있으면 색인 제외 → 제거)</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;한화손보다이렉트 주택화재보험 | 스크린홀인원·임시거주비&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>30자</t>
-        </is>
-      </c>
+          <t>&lt;meta name="robots" content="index,follow"&gt;  (또는 태그 없음=허용)</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr"/>
       <c r="J8" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
@@ -1566,7 +1562,7 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>주택화재보험</t>
+          <t>다이렉트 홈(메인)</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
@@ -1576,39 +1572,35 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>한화손보다이렉트 직접</t>
+          <t>메인</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
+          <t>https://m.hanwhadirect.com/</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
+          <t>사이트맵 제출·웹마스터도구/서치어드바이저 등록</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+          <t># sitemap.xml 미제출 → 하위 상품 페이지 색인 누락 가능</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="화재·누수·풍수재 피해와 임시거주비는 물론 스크린홀인원 담보까지. 한화손보다이렉트 주택화재보험을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>76자</t>
-        </is>
-      </c>
+          <t># sitemap.xml(하위 URL·lastmod·changefreq·priority) 작성 후 네이버 웹마스터도구 요청&gt;사이트맵 제출 / 구글 Search Console 등록</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr"/>
       <c r="J9" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
@@ -1618,40 +1610,192 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
+          <t>다이렉트 홈(메인)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>메인</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>상품 이미지 alt 텍스트 보강</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/home_cover.png"&gt;</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/home_cover.png" alt="다이렉트 홈(메인) 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr"/>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
           <t>주택화재보험</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>&lt;title&gt; 교체</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;화재&gt;고객정보입력&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보다이렉트 주택화재보험 | 스크린홀인원·임시거주비&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>30자</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>주택화재보험</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="화재·누수·풍수재 피해와 임시거주비는 물론 스크린홀인원 담보까지. 한화손보다이렉트 주택화재보험을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>76자</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>주택화재보험</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="화재보험에 스크린홀인원까지 — 한화손보다이렉트 주택화재보험"&gt;
 &lt;meta property="og:description" content="임시거주비에 스크린홀인원 담보까지 챙기는 주택화재보험을 3분 만에 설계하고 공유해요."&gt;
@@ -1659,204 +1803,56 @@
 &lt;meta property="og:url" content="https://m.hanwhadirect.com/ltr/hrmf/main.do"&gt;</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr"/>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr"/>
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>주택화재보험</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>모바일(m.)·PC(www) 메타 일치 + canonical</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- m./www 메타 상이·canonical 누락 가능 --&gt;</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>&lt;link rel="canonical" href="https://www.hanwhadirect.com/ltr/hrmf/main.do"&gt;
 &lt;link rel="alternate" media="only screen and (max-width: 640px)" href="https://m.hanwhadirect.com/ltr/hrmf/main.do"&gt;</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr"/>
-      <c r="J11" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>주택화재보험</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>H1을 상품명으로 1회만 지정</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>&lt;div class="logo"&gt;한화손보다이렉트&lt;/div&gt;  &lt;!-- h1이 로고/스텝인 경우 --&gt;</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;주택화재보험 — 119주택화재보험(스크린홀인원 담보)&lt;/h1&gt;</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr"/>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>주택화재보험</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/hrmf_cover.png"&gt;</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/hrmf_cover.png" alt="주택화재보험 보장내용 안내"&gt;</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr"/>
-      <c r="J13" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>골프보험</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/golf/</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>&lt;title&gt; 교체</t>
-        </is>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;골프&gt;고객정보입력&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;한화손보다이렉트 골프보험 | 홀인원·배상책임 보장&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>27자</t>
-        </is>
-      </c>
+      <c r="I14" s="12" t="inlineStr"/>
       <c r="J14" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
@@ -1866,7 +1862,7 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>골프보험</t>
+          <t>주택화재보험</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
@@ -1881,34 +1877,30 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/ltr/golf/</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
+          <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
+          <t>H1을 상품명으로 1회만 지정</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+          <t>&lt;div class="logo"&gt;한화손보다이렉트&lt;/div&gt;  &lt;!-- h1이 로고/스텝인 경우 --&gt;</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="홀인원 축하비용부터 타인 상해 배상책임까지. 한화손보다이렉트 골프보험으로 라운딩 중 위험을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>73자</t>
-        </is>
-      </c>
+          <t>&lt;h1&gt;주택화재보험 — 119주택화재보험(스크린홀인원 담보)&lt;/h1&gt;</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr"/>
       <c r="J15" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
@@ -1918,40 +1910,192 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
+          <t>주택화재보험</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>상품 이미지 alt 텍스트 보강</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/hrmf_cover.png"&gt;</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/hrmf_cover.png" alt="주택화재보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr"/>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
           <t>골프보험</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/golf/</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>&lt;title&gt; 교체</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;골프&gt;고객정보입력&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보다이렉트 골프보험 | 홀인원·배상책임 보장&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>27자</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>골프보험</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/golf/</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="홀인원 축하비용부터 타인 상해 배상책임까지. 한화손보다이렉트 골프보험으로 라운딩 중 위험을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>73자</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>골프보험</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/golf/</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="홀인원, 축하만큼 비용도 크다 — 한화손보다이렉트 골프보험"&gt;
 &lt;meta property="og:description" content="라운딩 중 사고·배상책임·홀인원 비용까지. 3분 만에 설계하고 동반자와 공유해요."&gt;
@@ -1959,204 +2103,56 @@
 &lt;meta property="og:url" content="https://m.hanwhadirect.com/ltr/golf/"&gt;</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr"/>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr"/>
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>골프보험</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/golf/</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>모바일(m.)·PC(www) 메타 일치 + canonical</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- m./www 메타 상이·canonical 누락 가능 --&gt;</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>&lt;link rel="canonical" href="https://www.hanwhadirect.com/ltr/golf/"&gt;
 &lt;link rel="alternate" media="only screen and (max-width: 640px)" href="https://m.hanwhadirect.com/ltr/golf/"&gt;</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>골프보험</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/golf/</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>H1을 상품명으로 1회만 지정</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>&lt;div class="logo"&gt;한화손보다이렉트&lt;/div&gt;  &lt;!-- h1이 로고/스텝인 경우 --&gt;</t>
-        </is>
-      </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;골프보험 — 홀인원·배상책임&lt;/h1&gt;</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr"/>
-      <c r="J18" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>골프보험</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/golf/</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/golf_cover.png"&gt;</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/golf_cover.png" alt="골프보험 보장내용 안내"&gt;</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr"/>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>암보험</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/cncr/</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>&lt;title&gt; 교체</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;암&gt;고객정보입력 - 메인&gt;다이렉트 홈&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;한화손보다이렉트 내가고른 암보험 | 4대유사암 단독가입&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>30자</t>
-        </is>
-      </c>
+      <c r="I20" s="12" t="inlineStr"/>
       <c r="J20" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
@@ -2166,7 +2162,7 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>암보험</t>
+          <t>골프보험</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
@@ -2181,34 +2177,30 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/ltr/cncr/</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
+          <t>https://m.hanwhadirect.com/ltr/golf/</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
+          <t>H1을 상품명으로 1회만 지정</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="이 상품을 꼭 가입하셔야 하는 이유 … 확인필-제2026-장기CM사업부-기타(광고)01545L…"&gt;</t>
+          <t>&lt;div class="logo"&gt;한화손보다이렉트&lt;/div&gt;  &lt;!-- h1이 로고/스텝인 경우 --&gt;</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="필요한 담보만 직접 고르는 한화손보다이렉트 암보험. 4대 유사암 단독 가입과 진단·수술·입원비 보장을 온라인에서 설계·비교해 보세요."&gt;</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>74자</t>
-        </is>
-      </c>
+          <t>&lt;h1&gt;골프보험 — 홀인원·배상책임&lt;/h1&gt;</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr"/>
       <c r="J21" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
@@ -2218,40 +2210,192 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>골프보험</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/golf/</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>상품 이미지 alt 텍스트 보강</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/golf_cover.png"&gt;</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/golf_cover.png" alt="골프보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr"/>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
           <t>암보험</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/cncr/</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>&lt;title&gt; 교체</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;암&gt;고객정보입력 - 메인&gt;다이렉트 홈&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보다이렉트 내가고른 암보험 | 4대유사암 단독가입&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>30자</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>암보험</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/cncr/</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="이 상품을 꼭 가입하셔야 하는 이유 … 확인필-제2026-장기CM사업부-기타(광고)01545L…"&gt;</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="필요한 담보만 직접 고르는 한화손보다이렉트 암보험. 4대 유사암 단독 가입과 진단·수술·입원비 보장을 온라인에서 설계·비교해 보세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>74자</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>암보험</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/cncr/</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="내 암보험, 담보는 내가 고른다 — 한화손보다이렉트"&gt;
 &lt;meta property="og:description" content="필요한 보장만 골라 담고 불필요한 특약은 빼고. 카톡으로 공유하고 보험료까지 3분 안에 확인해요."&gt;
@@ -2259,204 +2403,56 @@
 &lt;meta property="og:url" content="https://m.hanwhadirect.com/ltr/cncr/"&gt;</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr"/>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr"/>
+      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>암보험</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/cncr/</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>모바일(m.)·PC(www) 메타 일치 + canonical</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- m./www 메타 상이·canonical 누락 가능 --&gt;</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H26" s="14" t="inlineStr">
         <is>
           <t>&lt;link rel="canonical" href="https://www.hanwhadirect.com/ltr/cncr/"&gt;
 &lt;link rel="alternate" media="only screen and (max-width: 640px)" href="https://m.hanwhadirect.com/ltr/cncr/"&gt;</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr"/>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>암보험</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/cncr/</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>H1을 상품명으로 1회만 지정</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>&lt;div class="logo"&gt;한화손보다이렉트&lt;/div&gt;  &lt;!-- h1이 로고/스텝인 경우 --&gt;</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;내가고른 암보험 — 담보 선택형&lt;/h1&gt;</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="inlineStr"/>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>암보험</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/cncr/</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/cncr_cover.png"&gt;</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/cncr_cover.png" alt="암보험 보장내용 안내"&gt;</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="inlineStr"/>
-      <c r="J25" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>치아보험</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/dntl/</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>&lt;meta name="description" content="충치·치주질환 치료비부터 스케일링까지. 한화손보다이렉트 치아안심보험의 보존·보철 보장과 보험료를 온라인에서 바로 확인하세요."&gt;</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>69자</t>
-        </is>
-      </c>
+      <c r="I26" s="12" t="inlineStr"/>
       <c r="J26" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
@@ -2466,7 +2462,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>치아보험</t>
+          <t>암보험</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
@@ -2481,7 +2477,7 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/ltr/dntl/</t>
+          <t>https://m.hanwhadirect.com/ltr/cncr/</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -2491,24 +2487,20 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>&lt;title&gt; 교체</t>
+          <t>H1을 상품명으로 1회만 지정</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;한화손해보험 다이렉트 치아안심보험 무배당2504&lt;/title&gt;</t>
+          <t>&lt;div class="logo"&gt;한화손보다이렉트&lt;/div&gt;  &lt;!-- h1이 로고/스텝인 경우 --&gt;</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;한화손보다이렉트 치아안심보험 | 스케일링·보철 보장&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>28자</t>
-        </is>
-      </c>
+          <t>&lt;h1&gt;내가고른 암보험 — 담보 선택형&lt;/h1&gt;</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr"/>
       <c r="J27" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
@@ -2518,40 +2510,192 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
+          <t>암보험</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/cncr/</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>상품 이미지 alt 텍스트 보강</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/cncr_cover.png"&gt;</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/cncr_cover.png" alt="암보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr"/>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
           <t>치아보험</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/dntl/</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="충치·치주질환 치료비부터 스케일링까지. 한화손보다이렉트 치아안심보험의 보존·보철 보장과 보험료를 온라인에서 바로 확인하세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>69자</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>치아보험</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/dntl/</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>&lt;title&gt; 교체</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손해보험 다이렉트 치아안심보험 무배당2504&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보다이렉트 치아안심보험 | 스케일링·보철 보장&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>28자</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>치아보험</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/dntl/</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="스케일링부터 임플란트까지 — 한화손보다이렉트 치아보험"&gt;
 &lt;meta property="og:description" content="미루기 쉬운 치과 치료비, 미리 준비해요. 보장과 보험료를 3분 만에 확인하고 카톡으로 공유하세요."&gt;
@@ -2559,301 +2703,301 @@
 &lt;meta property="og:url" content="https://m.hanwhadirect.com/ltr/dntl/"&gt;</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr"/>
-      <c r="J28" s="12" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr"/>
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>치아보험</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/dntl/</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>모바일(m.)·PC(www) 메타 일치 + canonical</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- m./www 메타 상이·canonical 누락 가능 --&gt;</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
         <is>
           <t>&lt;link rel="canonical" href="https://www.hanwhadirect.com/ltr/dntl/"&gt;
 &lt;link rel="alternate" media="only screen and (max-width: 640px)" href="https://m.hanwhadirect.com/ltr/dntl/"&gt;</t>
         </is>
       </c>
-      <c r="I29" s="12" t="inlineStr"/>
-      <c r="J29" s="12" t="inlineStr">
+      <c r="I32" s="12" t="inlineStr"/>
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>치아보험</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/dntl/</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>&lt;img src="/img/dntl_cover.png"&gt;</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>&lt;img src="/img/dntl_cover.png" alt="치아보험 보장내용 안내"&gt;</t>
         </is>
       </c>
-      <c r="I30" s="12" t="inlineStr"/>
-      <c r="J30" s="12" t="inlineStr">
+      <c r="I33" s="12" t="inlineStr"/>
+      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>운전자보험</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=driver</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>&lt;meta name="description"&gt; 신설/교체</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>&lt;meta name="description" content="자동차보험, 운전자보험, 해외여행보험 등 가입부터 관리까지 비대면으로 간편하게 가입. 한화손보…"&gt;</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H34" s="14" t="inlineStr">
         <is>
           <t>&lt;meta name="description" content="교통사고 벌금·변호사선임비·형사합의금까지. 한화손보 캐롯 운전자보험을 온라인에서 필요한 담보만 골라 설계하고 보험료를 확인하세요."&gt;</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>72자</t>
         </is>
       </c>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/long-term/driver</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>운전자보험</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=driver</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>분기(carrotBridge) 색인·canonical 정리</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- /cmcom/carrotBridge.do?carrot=driver : 302(추정) 이동·canonical 없음·campaignId 중복 --&gt;</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- 목적지가 정본이면 301 + canonical 통일 --&gt;
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>분기(carrotBridge) 리다이렉트·canonical 정리</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- /cmcom/carrotBridge.do?carrot=driver : JS/meta refresh·302 금지 · canonical 없음 · campaignId 중복 --&gt;</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- 서버 HTTP 301(Location)로 이동 + 목적지 canonical 통일 --&gt;
 &lt;link rel="canonical" href="https://www.carrotins.com/long-term/driver"&gt;
 &lt;!-- 또는 CM이 랭킹 확보시 hanwhadirect에 상품 콘텐츠 랜딩 신설 --&gt;</t>
         </is>
       </c>
-      <c r="I32" s="12" t="inlineStr"/>
-      <c r="J32" s="12" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr"/>
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/long-term/driver</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>운전자보험</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=driver</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>&lt;title&gt; 교체</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>&lt;title&gt;캐롯 운전자보험 무배당2604&lt;/title&gt;</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="H36" s="14" t="inlineStr">
         <is>
           <t>&lt;title&gt;한화손보 캐롯 운전자보험 | 벌금·변호사·합의금 보장&lt;/title&gt;</t>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>29자</t>
         </is>
       </c>
-      <c r="J33" s="12" t="inlineStr">
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/long-term/driver</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>운전자보험</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=driver</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H37" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="사고는 순간, 비용은 오래 간다 — 한화손보 캐롯 운전자보험"&gt;
 &lt;meta property="og:description" content="벌금·변호사비·합의금까지 대비하는 운전자보험. 3분 만에 담보를 골라 설계하고 카톡으로 공유해요."&gt;
@@ -2861,252 +3005,252 @@
 &lt;meta property="og:url" content="https://www.carrotins.com/long-term/driver"&gt;</t>
         </is>
       </c>
-      <c r="I34" s="12" t="inlineStr"/>
-      <c r="J34" s="12" t="inlineStr">
+      <c r="I37" s="12" t="inlineStr"/>
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/long-term/driver</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>운전자보험</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=driver</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>&lt;img src="/img/driver_cover.png"&gt;</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="H38" s="14" t="inlineStr">
         <is>
           <t>&lt;img src="/img/driver_cover.png" alt="운전자보험 보장내용 안내"&gt;</t>
         </is>
       </c>
-      <c r="I35" s="12" t="inlineStr"/>
-      <c r="J35" s="12" t="inlineStr">
+      <c r="I38" s="12" t="inlineStr"/>
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/long-term/driver</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>여성건강보험</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=woman</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>분기(carrotBridge) 색인·canonical 정리</t>
-        </is>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- /cmcom/carrotBridge.do?carrot=woman : 302(추정) 이동·canonical 없음·campaignId 중복 --&gt;</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- 목적지가 정본이면 301 + canonical 통일 --&gt;
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>분기(carrotBridge) 리다이렉트·canonical 정리</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- /cmcom/carrotBridge.do?carrot=woman : JS/meta refresh·302 금지 · canonical 없음 · campaignId 중복 --&gt;</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- 서버 HTTP 301(Location)로 이동 + 목적지 canonical 통일 --&gt;
 &lt;link rel="canonical" href="https://www.carrotins.com/long-term/women-signature/"&gt;
 &lt;!-- 또는 CM이 랭킹 확보시 hanwhadirect에 상품 콘텐츠 랜딩 신설 --&gt;</t>
         </is>
       </c>
-      <c r="I36" s="12" t="inlineStr"/>
-      <c r="J36" s="12" t="inlineStr">
+      <c r="I39" s="12" t="inlineStr"/>
+      <c r="J39" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/long-term/women-signature/</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>여성건강보험</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=woman</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>&lt;title&gt; 교체</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>&lt;title&gt;한화 다이렉트 시그니처 여성 건강보험4.0(무)&lt;/title&gt;</t>
         </is>
       </c>
-      <c r="H37" s="14" t="inlineStr">
+      <c r="H40" s="14" t="inlineStr">
         <is>
           <t>&lt;title&gt;한화손보 캐롯 여성건강보험 | 임신·출산·산후조리 지원&lt;/title&gt;</t>
         </is>
       </c>
-      <c r="I37" s="12" t="inlineStr">
+      <c r="I40" s="12" t="inlineStr">
         <is>
           <t>30자</t>
         </is>
       </c>
-      <c r="J37" s="12" t="inlineStr">
+      <c r="J40" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/long-term/women-signature/</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>여성건강보험</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=woman</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>&lt;meta name="description"&gt; 신설/교체</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>&lt;meta name="description" content="아이가 생기고, 출산은 물론 산후조리원비용까지 지급해요. 임신지원금(1회한), 출산지원금(세부…"&gt;</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>&lt;meta name="description" content="임신·출산지원금부터 산후조리원 비용까지. 한화손보 캐롯 시그니처 여성건강보험4.0의 여성 특화 보장을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
         </is>
       </c>
-      <c r="I38" s="12" t="inlineStr">
+      <c r="I41" s="12" t="inlineStr">
         <is>
           <t>79자</t>
         </is>
       </c>
-      <c r="J38" s="12" t="inlineStr">
+      <c r="J41" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/long-term/women-signature/</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>여성건강보험</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=woman</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr">
+      <c r="H42" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="임신부터 산후조리까지, 여성을 위한 설계 — 한화손보 캐롯"&gt;
 &lt;meta property="og:description" content="출산지원금과 산후조리원 비용까지 챙기는 여성건강보험. 3분 만에 설계하고 카톡으로 공유해요."&gt;
@@ -3114,252 +3258,252 @@
 &lt;meta property="og:url" content="https://www.carrotins.com/long-term/women-signature/"&gt;</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr"/>
-      <c r="J39" s="12" t="inlineStr">
+      <c r="I42" s="12" t="inlineStr"/>
+      <c r="J42" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/long-term/women-signature/</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>여성건강보험</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>한화손보 캐롯</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>캐롯 분기</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=woman</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/woman_cover.png"&gt;</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/woman_cover.png" alt="여성건강보험 보장내용 안내"&gt;</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="inlineStr"/>
-      <c r="J40" s="12" t="inlineStr">
-        <is>
-          <t>목적지: https://www.carrotins.com/long-term/women-signature/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>임신·출산(태아)보험</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>한화손보 캐롯</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>캐롯 분기</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=birth</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>&lt;title&gt; 교체</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;(전용 색인 노출 약함 — 태아보험 SERP를 경쟁사가 점유)&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;한화손보 캐롯 태아보험 | 임신·출산·선천이상 보장&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>28자</t>
-        </is>
-      </c>
-      <c r="J41" s="12" t="inlineStr">
-        <is>
-          <t>목적지: https://www.carrotins.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>임신·출산(태아)보험</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>한화손보 캐롯</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>캐롯 분기</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=birth</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
-        </is>
-      </c>
-      <c r="H42" s="14" t="inlineStr">
-        <is>
-          <t>&lt;meta name="description" content="임신 중 가입부터 미숙아·선천이상 수술·입원 보장까지. 한화손보 캐롯 태아보험을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>67자</t>
-        </is>
-      </c>
-      <c r="J42" s="12" t="inlineStr">
-        <is>
-          <t>목적지: https://www.carrotins.com/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
+          <t>여성건강보험</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=woman</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>상품 이미지 alt 텍스트 보강</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/woman_cover.png"&gt;</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/woman_cover.png" alt="여성건강보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr"/>
+      <c r="J43" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/long-term/women-signature/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
           <t>임신·출산(태아)보험</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=birth</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>분기(carrotBridge) 색인·canonical 정리</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- /cmcom/carrotBridge.do?carrot=birth : 302(추정) 이동·canonical 없음·campaignId 중복 --&gt;</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- 목적지가 정본이면 301 + canonical 통일 --&gt;
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>&lt;title&gt; 교체</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;(전용 색인 노출 약함 — 태아보험 SERP를 경쟁사가 점유)&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보 캐롯 태아보험 | 임신·출산·선천이상 보장&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>28자</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>임신·출산(태아)보험</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=birth</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="임신 중 가입부터 미숙아·선천이상 수술·입원 보장까지. 한화손보 캐롯 태아보험을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>67자</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>임신·출산(태아)보험</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=birth</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>분기(carrotBridge) 리다이렉트·canonical 정리</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- /cmcom/carrotBridge.do?carrot=birth : JS/meta refresh·302 금지 · canonical 없음 · campaignId 중복 --&gt;</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- 서버 HTTP 301(Location)로 이동 + 목적지 canonical 통일 --&gt;
 &lt;link rel="canonical" href="https://www.carrotins.com/"&gt;
 &lt;!-- 또는 CM이 랭킹 확보시 hanwhadirect에 상품 콘텐츠 랜딩 신설 --&gt;</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr"/>
-      <c r="J43" s="12" t="inlineStr">
+      <c r="I46" s="12" t="inlineStr"/>
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>임신·출산(태아)보험</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=birth</t>
         </is>
       </c>
-      <c r="E44" s="15" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G44" s="14" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr">
+      <c r="H47" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="엄마가 되기 전에, 태아보험부터 — 한화손보 캐롯"&gt;
 &lt;meta property="og:description" content="임신 22주 전 가입·태아 특약까지. 3분 만에 설계하고 카톡으로 공유해요."&gt;
@@ -3367,252 +3511,252 @@
 &lt;meta property="og:url" content="https://www.carrotins.com/"&gt;</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr"/>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="I47" s="12" t="inlineStr"/>
+      <c r="J47" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>임신·출산(태아)보험</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=birth</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
-      <c r="G45" s="14" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>&lt;img src="/img/birth_cover.png"&gt;</t>
         </is>
       </c>
-      <c r="H45" s="14" t="inlineStr">
+      <c r="H48" s="14" t="inlineStr">
         <is>
           <t>&lt;img src="/img/birth_cover.png" alt="임신·출산(태아)보험 보장내용 안내"&gt;</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr"/>
-      <c r="J45" s="12" t="inlineStr">
+      <c r="I48" s="12" t="inlineStr"/>
+      <c r="J48" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>해외여행보험</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>&lt;meta name="description"&gt; 신설/교체</t>
         </is>
       </c>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>&lt;meta name="description" content="출국 7일 이전 가입 ; 2명 이상 함께 가입 ; 10% 환급 ; 고객님께 안내드립니다. 전쟁…"&gt;</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr">
+      <c r="H49" s="14" t="inlineStr">
         <is>
           <t>&lt;meta name="description" content="출국 전 간편 가입과 무사고 시 캐시백까지. 한화손보 캐롯 해외여행보험을 개인정보 없이 온라인에서 비교하고 보험료를 확인하세요."&gt;</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
+      <c r="I49" s="12" t="inlineStr">
         <is>
           <t>71자</t>
         </is>
       </c>
-      <c r="J46" s="12" t="inlineStr">
+      <c r="J49" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/product/overseas</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>해외여행보험</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>분기(carrotBridge) 색인·canonical 정리</t>
-        </is>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- /cmcom/carrotBridge.do?carrot=overseas : 302(추정) 이동·canonical 없음·campaignId 중복 --&gt;</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- 목적지가 정본이면 301 + canonical 통일 --&gt;
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>분기(carrotBridge) 리다이렉트·canonical 정리</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- /cmcom/carrotBridge.do?carrot=overseas : JS/meta refresh·302 금지 · canonical 없음 · campaignId 중복 --&gt;</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- 서버 HTTP 301(Location)로 이동 + 목적지 canonical 통일 --&gt;
 &lt;link rel="canonical" href="https://www.carrotins.com/product/overseas"&gt;
 &lt;!-- 또는 CM이 랭킹 확보시 hanwhadirect에 상품 콘텐츠 랜딩 신설 --&gt;</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr"/>
-      <c r="J47" s="12" t="inlineStr">
+      <c r="I50" s="12" t="inlineStr"/>
+      <c r="J50" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/product/overseas</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>해외여행보험</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas</t>
         </is>
       </c>
-      <c r="E48" s="15" t="inlineStr">
+      <c r="E51" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr">
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>&lt;title&gt; 교체</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
+      <c r="G51" s="14" t="inlineStr">
         <is>
           <t>&lt;title&gt;한화손보 캐롯 해외여행보험 | 여행자 보험료 개인정보 없이 간편 확인&lt;/title&gt;</t>
         </is>
       </c>
-      <c r="H48" s="14" t="inlineStr">
+      <c r="H51" s="14" t="inlineStr">
         <is>
           <t>&lt;title&gt;한화손보 캐롯 해외여행보험 | 개인정보 없이 보험료 확인&lt;/title&gt;</t>
         </is>
       </c>
-      <c r="I48" s="12" t="inlineStr">
+      <c r="I51" s="12" t="inlineStr">
         <is>
           <t>31자</t>
         </is>
       </c>
-      <c r="J48" s="12" t="inlineStr">
+      <c r="J51" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/product/overseas</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>해외여행보험</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas</t>
         </is>
       </c>
-      <c r="E49" s="16" t="inlineStr">
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="G52" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H49" s="14" t="inlineStr">
+      <c r="H52" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="여행 전 3분, 한화손보 캐롯 해외여행보험"&gt;
 &lt;meta property="og:description" content="출국 전 간편가입·무사고 캐시백. 개인정보 없이 보험료를 바로 확인해요."&gt;
@@ -3620,252 +3764,252 @@
 &lt;meta property="og:url" content="https://www.carrotins.com/product/overseas"&gt;</t>
         </is>
       </c>
-      <c r="I49" s="12" t="inlineStr"/>
-      <c r="J49" s="12" t="inlineStr">
+      <c r="I52" s="12" t="inlineStr"/>
+      <c r="J52" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/product/overseas</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>해외여행보험</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas</t>
         </is>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E53" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>&lt;img src="/img/overseas_cover.png"&gt;</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr">
+      <c r="H53" s="14" t="inlineStr">
         <is>
           <t>&lt;img src="/img/overseas_cover.png" alt="해외여행보험 보장내용 안내"&gt;</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr"/>
-      <c r="J50" s="12" t="inlineStr">
+      <c r="I53" s="12" t="inlineStr"/>
+      <c r="J53" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/product/overseas</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>해외장기체류보험</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>&lt;meta name="description"&gt; 신설/교체</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="G54" s="14" t="inlineStr">
         <is>
           <t>&lt;meta name="description" content="해외체류 중 질병이나 상해를 입어 해외의료기관에서 치료를 받은 경우 최대 10만달러까지 보장해…"&gt;</t>
         </is>
       </c>
-      <c r="H51" s="14" t="inlineStr">
+      <c r="H54" s="14" t="inlineStr">
         <is>
           <t>&lt;meta name="description" content="3개월 초과 해외체류·유학 중 질병·상해 의료비를 최대 10만달러까지. 한화손보 캐롯 해외장기체류보험을 온라인에서 확인하세요."&gt;</t>
         </is>
       </c>
-      <c r="I51" s="12" t="inlineStr">
+      <c r="I54" s="12" t="inlineStr">
         <is>
           <t>70자</t>
         </is>
       </c>
-      <c r="J51" s="12" t="inlineStr">
+      <c r="J54" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>해외장기체류보험</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
-        <is>
-          <t>분기(carrotBridge) 색인·canonical 정리</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- /cmcom/carrotBridge.do?carrot=overseas-long : 302(추정) 이동·canonical 없음·campaignId 중복 --&gt;</t>
-        </is>
-      </c>
-      <c r="H52" s="14" t="inlineStr">
-        <is>
-          <t>&lt;!-- 목적지가 정본이면 301 + canonical 통일 --&gt;
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>분기(carrotBridge) 리다이렉트·canonical 정리</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- /cmcom/carrotBridge.do?carrot=overseas-long : JS/meta refresh·302 금지 · canonical 없음 · campaignId 중복 --&gt;</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- 서버 HTTP 301(Location)로 이동 + 목적지 canonical 통일 --&gt;
 &lt;link rel="canonical" href="https://www.carrotins.com/product/overseas-long/intro"&gt;
 &lt;!-- 또는 CM이 랭킹 확보시 hanwhadirect에 상품 콘텐츠 랜딩 신설 --&gt;</t>
         </is>
       </c>
-      <c r="I52" s="12" t="inlineStr"/>
-      <c r="J52" s="12" t="inlineStr">
+      <c r="I55" s="12" t="inlineStr"/>
+      <c r="J55" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>해외장기체류보험</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
         </is>
       </c>
-      <c r="E53" s="15" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F56" s="12" t="inlineStr">
         <is>
           <t>&lt;title&gt; 교체</t>
         </is>
       </c>
-      <c r="G53" s="14" t="inlineStr">
+      <c r="G56" s="14" t="inlineStr">
         <is>
           <t>&lt;title&gt;한화손보 캐롯 해외장기체류보험 | 3개월 초과 여행, 장기 유학시 보장&lt;/title&gt;</t>
         </is>
       </c>
-      <c r="H53" s="14" t="inlineStr">
+      <c r="H56" s="14" t="inlineStr">
         <is>
           <t>&lt;title&gt;한화손보 캐롯 해외장기체류보험 | 유학·장기체류 보장&lt;/title&gt;</t>
         </is>
       </c>
-      <c r="I53" s="12" t="inlineStr">
+      <c r="I56" s="12" t="inlineStr">
         <is>
           <t>29자</t>
         </is>
       </c>
-      <c r="J53" s="12" t="inlineStr">
+      <c r="J56" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>해외장기체류보험</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
         </is>
       </c>
-      <c r="E54" s="16" t="inlineStr">
+      <c r="E57" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F54" s="12" t="inlineStr">
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G54" s="14" t="inlineStr">
+      <c r="G57" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H54" s="14" t="inlineStr">
+      <c r="H57" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="유학·장기출장 전 필수 — 한화손보 캐롯 해외장기체류보험"&gt;
 &lt;meta property="og:description" content="3개월 넘는 해외체류, 현지 의료비까지 대비하는 장기체류보험. 개인정보 없이 보험료를 확인해요."&gt;
@@ -3873,63 +4017,63 @@
 &lt;meta property="og:url" content="https://www.carrotins.com/product/overseas-long/intro"&gt;</t>
         </is>
       </c>
-      <c r="I54" s="12" t="inlineStr"/>
-      <c r="J54" s="12" t="inlineStr">
+      <c r="I57" s="12" t="inlineStr"/>
+      <c r="J57" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>해외장기체류보험</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
         </is>
       </c>
-      <c r="E55" s="16" t="inlineStr">
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>&lt;img src="/img/overseaslong_cover.png"&gt;</t>
         </is>
       </c>
-      <c r="H55" s="14" t="inlineStr">
+      <c r="H58" s="14" t="inlineStr">
         <is>
           <t>&lt;img src="/img/overseaslong_cover.png" alt="해외장기체류보험 보장내용 안내"&gt;</t>
         </is>
       </c>
-      <c r="I55" s="12" t="inlineStr"/>
-      <c r="J55" s="12" t="inlineStr">
+      <c r="I58" s="12" t="inlineStr"/>
+      <c r="J58" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J55"/>
+  <autoFilter ref="A1:J58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/handoff/한화손보_장기CM_태깅가이드.xlsx
+++ b/handoff/한화손보_장기CM_태깅가이드.xlsx
@@ -10,9 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="태깅가이드" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카피안" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="네이버_웹표준체크리스트" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'태깅가이드'!$A$1:$J$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'태깅가이드'!$A$1:$J$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +67,20 @@
     <font>
       <name val="Consolas"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00B4242A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000F7A37"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
   <fills count="6">
@@ -122,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,6 +180,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1129,7 +1150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1635,17 +1656,17 @@
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
+          <t>연관 채널 구조화 데이터 (선택·고급)</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>&lt;img src="/img/home_cover.png"&gt;</t>
+          <t>&lt;!-- 연관 채널(블로그·SNS) 구조화 데이터 없음 --&gt;</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>&lt;img src="/img/home_cover.png" alt="다이렉트 홈(메인) 보장내용 안내"&gt;</t>
+          <t>&lt;script type="application/ld+json"&gt;{"@context":"https://schema.org","@type":"Organization","name":"한화손해보험 다이렉트","url":"https://www.hanwhadirect.com/","sameAs":["https://blog.naver.com/hwgi01","인스타/유튜브 공식채널"]}&lt;/script&gt;</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr"/>
@@ -1658,7 +1679,7 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>주택화재보험</t>
+          <t>다이렉트 홈(메인)</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
@@ -1668,39 +1689,35 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>한화손보다이렉트 직접</t>
+          <t>메인</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
+          <t>https://m.hanwhadirect.com/</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>&lt;title&gt; 교체</t>
+          <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;화재&gt;고객정보입력&lt;/title&gt;</t>
+          <t>&lt;img src="/img/home_cover.png"&gt;</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;한화손보다이렉트 주택화재보험 | 스크린홀인원·임시거주비&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>30자</t>
-        </is>
-      </c>
+          <t>&lt;img src="/img/home_cover.png" alt="다이렉트 홈(메인) 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr"/>
       <c r="J11" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
@@ -1735,22 +1752,22 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
+          <t>&lt;title&gt; 교체</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+          <t>&lt;title&gt;화재&gt;고객정보입력&lt;/title&gt;</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="화재·누수·풍수재 피해와 임시거주비는 물론 스크린홀인원 담보까지. 한화손보다이렉트 주택화재보험을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
+          <t>&lt;title&gt;한화손보다이렉트 주택화재보험 | 스크린홀인원·임시거주비&lt;/title&gt;</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>76자</t>
+          <t>30자</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
@@ -1780,22 +1797,74 @@
           <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="화재·누수·풍수재 피해와 임시거주비는 물론 스크린홀인원 담보까지. 한화손보다이렉트 주택화재보험을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>76자</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>주택화재보험</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="화재보험에 스크린홀인원까지 — 한화손보다이렉트 주택화재보험"&gt;
 &lt;meta property="og:description" content="임시거주비에 스크린홀인원 담보까지 챙기는 주택화재보험을 3분 만에 설계하고 공유해요."&gt;
@@ -1803,103 +1872,55 @@
 &lt;meta property="og:url" content="https://m.hanwhadirect.com/ltr/hrmf/main.do"&gt;</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr"/>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr"/>
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>주택화재보험</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>모바일(m.)·PC(www) 메타 일치 + canonical</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- m./www 메타 상이·canonical 누락 가능 --&gt;</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>&lt;link rel="canonical" href="https://www.hanwhadirect.com/ltr/hrmf/main.do"&gt;
 &lt;link rel="alternate" media="only screen and (max-width: 640px)" href="https://m.hanwhadirect.com/ltr/hrmf/main.do"&gt;</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr"/>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>주택화재보험</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>H1을 상품명으로 1회만 지정</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>&lt;div class="logo"&gt;한화손보다이렉트&lt;/div&gt;  &lt;!-- h1이 로고/스텝인 경우 --&gt;</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;주택화재보험 — 119주택화재보험(스크린홀인원 담보)&lt;/h1&gt;</t>
-        </is>
-      </c>
       <c r="I15" s="12" t="inlineStr"/>
       <c r="J15" s="12" t="inlineStr">
         <is>
@@ -1928,24 +1949,24 @@
           <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
+          <t>H1을 상품명으로 1회만 지정</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>&lt;img src="/img/hrmf_cover.png"&gt;</t>
+          <t>&lt;div class="logo"&gt;한화손보다이렉트&lt;/div&gt;  &lt;!-- h1이 로고/스텝인 경우 --&gt;</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>&lt;img src="/img/hrmf_cover.png" alt="주택화재보험 보장내용 안내"&gt;</t>
+          <t>&lt;h1&gt;주택화재보험 — 119주택화재보험(스크린홀인원 담보)&lt;/h1&gt;</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr"/>
@@ -1958,7 +1979,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>골프보험</t>
+          <t>주택화재보험</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
@@ -1973,34 +1994,30 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/ltr/golf/</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
+          <t>https://m.hanwhadirect.com/ltr/hrmf/main.do</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>&lt;title&gt; 교체</t>
+          <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;골프&gt;고객정보입력&lt;/title&gt;</t>
+          <t>&lt;img src="/img/hrmf_cover.png"&gt;</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;한화손보다이렉트 골프보험 | 홀인원·배상책임 보장&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>27자</t>
-        </is>
-      </c>
+          <t>&lt;img src="/img/hrmf_cover.png" alt="주택화재보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
@@ -2035,22 +2052,22 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
+          <t>&lt;title&gt; 교체</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+          <t>&lt;title&gt;골프&gt;고객정보입력&lt;/title&gt;</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="홀인원 축하비용부터 타인 상해 배상책임까지. 한화손보다이렉트 골프보험으로 라운딩 중 위험을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
+          <t>&lt;title&gt;한화손보다이렉트 골프보험 | 홀인원·배상책임 보장&lt;/title&gt;</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>73자</t>
+          <t>27자</t>
         </is>
       </c>
       <c r="J18" s="12" t="inlineStr">
@@ -2080,22 +2097,74 @@
           <t>https://m.hanwhadirect.com/ltr/golf/</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="홀인원 축하비용부터 타인 상해 배상책임까지. 한화손보다이렉트 골프보험으로 라운딩 중 위험을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>73자</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>골프보험</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/golf/</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="홀인원, 축하만큼 비용도 크다 — 한화손보다이렉트 골프보험"&gt;
 &lt;meta property="og:description" content="라운딩 중 사고·배상책임·홀인원 비용까지. 3분 만에 설계하고 동반자와 공유해요."&gt;
@@ -2103,103 +2172,55 @@
 &lt;meta property="og:url" content="https://m.hanwhadirect.com/ltr/golf/"&gt;</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr"/>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr"/>
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>골프보험</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/golf/</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>모바일(m.)·PC(www) 메타 일치 + canonical</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- m./www 메타 상이·canonical 누락 가능 --&gt;</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>&lt;link rel="canonical" href="https://www.hanwhadirect.com/ltr/golf/"&gt;
 &lt;link rel="alternate" media="only screen and (max-width: 640px)" href="https://m.hanwhadirect.com/ltr/golf/"&gt;</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr"/>
-      <c r="J20" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>골프보험</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/golf/</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>H1을 상품명으로 1회만 지정</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>&lt;div class="logo"&gt;한화손보다이렉트&lt;/div&gt;  &lt;!-- h1이 로고/스텝인 경우 --&gt;</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;골프보험 — 홀인원·배상책임&lt;/h1&gt;</t>
-        </is>
-      </c>
       <c r="I21" s="12" t="inlineStr"/>
       <c r="J21" s="12" t="inlineStr">
         <is>
@@ -2228,24 +2249,24 @@
           <t>https://m.hanwhadirect.com/ltr/golf/</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
+          <t>H1을 상품명으로 1회만 지정</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>&lt;img src="/img/golf_cover.png"&gt;</t>
+          <t>&lt;div class="logo"&gt;한화손보다이렉트&lt;/div&gt;  &lt;!-- h1이 로고/스텝인 경우 --&gt;</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>&lt;img src="/img/golf_cover.png" alt="골프보험 보장내용 안내"&gt;</t>
+          <t>&lt;h1&gt;골프보험 — 홀인원·배상책임&lt;/h1&gt;</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr"/>
@@ -2258,7 +2279,7 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>암보험</t>
+          <t>골프보험</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
@@ -2273,34 +2294,30 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/ltr/cncr/</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
+          <t>https://m.hanwhadirect.com/ltr/golf/</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>&lt;title&gt; 교체</t>
+          <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;암&gt;고객정보입력 - 메인&gt;다이렉트 홈&lt;/title&gt;</t>
+          <t>&lt;img src="/img/golf_cover.png"&gt;</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;한화손보다이렉트 내가고른 암보험 | 4대유사암 단독가입&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>30자</t>
-        </is>
-      </c>
+          <t>&lt;img src="/img/golf_cover.png" alt="골프보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
@@ -2335,22 +2352,22 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
+          <t>&lt;title&gt; 교체</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="이 상품을 꼭 가입하셔야 하는 이유 … 확인필-제2026-장기CM사업부-기타(광고)01545L…"&gt;</t>
+          <t>&lt;title&gt;암&gt;고객정보입력 - 메인&gt;다이렉트 홈&lt;/title&gt;</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="필요한 담보만 직접 고르는 한화손보다이렉트 암보험. 4대 유사암 단독 가입과 진단·수술·입원비 보장을 온라인에서 설계·비교해 보세요."&gt;</t>
+          <t>&lt;title&gt;한화손보다이렉트 내가고른 암보험 | 4대유사암 단독가입&lt;/title&gt;</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>74자</t>
+          <t>30자</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">
@@ -2380,22 +2397,74 @@
           <t>https://m.hanwhadirect.com/ltr/cncr/</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="이 상품을 꼭 가입하셔야 하는 이유 … 확인필-제2026-장기CM사업부-기타(광고)01545L…"&gt;</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="필요한 담보만 직접 고르는 한화손보다이렉트 암보험. 4대 유사암 단독 가입과 진단·수술·입원비 보장을 온라인에서 설계·비교해 보세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>74자</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>암보험</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/cncr/</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H26" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="내 암보험, 담보는 내가 고른다 — 한화손보다이렉트"&gt;
 &lt;meta property="og:description" content="필요한 보장만 골라 담고 불필요한 특약은 빼고. 카톡으로 공유하고 보험료까지 3분 안에 확인해요."&gt;
@@ -2403,103 +2472,55 @@
 &lt;meta property="og:url" content="https://m.hanwhadirect.com/ltr/cncr/"&gt;</t>
         </is>
       </c>
-      <c r="I25" s="12" t="inlineStr"/>
-      <c r="J25" s="12" t="inlineStr">
+      <c r="I26" s="12" t="inlineStr"/>
+      <c r="J26" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>암보험</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/cncr/</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>모바일(m.)·PC(www) 메타 일치 + canonical</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- m./www 메타 상이·canonical 누락 가능 --&gt;</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>&lt;link rel="canonical" href="https://www.hanwhadirect.com/ltr/cncr/"&gt;
 &lt;link rel="alternate" media="only screen and (max-width: 640px)" href="https://m.hanwhadirect.com/ltr/cncr/"&gt;</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr"/>
-      <c r="J26" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>암보험</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/cncr/</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>H1을 상품명으로 1회만 지정</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>&lt;div class="logo"&gt;한화손보다이렉트&lt;/div&gt;  &lt;!-- h1이 로고/스텝인 경우 --&gt;</t>
-        </is>
-      </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;내가고른 암보험 — 담보 선택형&lt;/h1&gt;</t>
-        </is>
-      </c>
       <c r="I27" s="12" t="inlineStr"/>
       <c r="J27" s="12" t="inlineStr">
         <is>
@@ -2528,24 +2549,24 @@
           <t>https://m.hanwhadirect.com/ltr/cncr/</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
+          <t>H1을 상품명으로 1회만 지정</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>&lt;img src="/img/cncr_cover.png"&gt;</t>
+          <t>&lt;div class="logo"&gt;한화손보다이렉트&lt;/div&gt;  &lt;!-- h1이 로고/스텝인 경우 --&gt;</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>&lt;img src="/img/cncr_cover.png" alt="암보험 보장내용 안내"&gt;</t>
+          <t>&lt;h1&gt;내가고른 암보험 — 담보 선택형&lt;/h1&gt;</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr"/>
@@ -2558,7 +2579,7 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>치아보험</t>
+          <t>암보험</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
@@ -2573,34 +2594,30 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/ltr/dntl/</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
+          <t>https://m.hanwhadirect.com/ltr/cncr/</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
+          <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+          <t>&lt;img src="/img/cncr_cover.png"&gt;</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="충치·치주질환 치료비부터 스케일링까지. 한화손보다이렉트 치아안심보험의 보존·보철 보장과 보험료를 온라인에서 바로 확인하세요."&gt;</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>69자</t>
-        </is>
-      </c>
+          <t>&lt;img src="/img/cncr_cover.png" alt="암보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr"/>
       <c r="J29" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
@@ -2628,29 +2645,29 @@
           <t>https://m.hanwhadirect.com/ltr/dntl/</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>&lt;title&gt; 교체</t>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;한화손해보험 다이렉트 치아안심보험 무배당2504&lt;/title&gt;</t>
+          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;한화손보다이렉트 치아안심보험 | 스케일링·보철 보장&lt;/title&gt;</t>
+          <t>&lt;meta name="description" content="충치·치주질환 치료비부터 스케일링까지. 한화손보다이렉트 치아안심보험의 보존·보철 보장과 보험료를 온라인에서 바로 확인하세요."&gt;</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>28자</t>
+          <t>69자</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
@@ -2687,15 +2704,67 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
+          <t>&lt;title&gt; 교체</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손해보험 다이렉트 치아안심보험 무배당2504&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보다이렉트 치아안심보험 | 스케일링·보철 보장&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>28자</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>치아보험</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>한화손보다이렉트 직접</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/ltr/dntl/</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="스케일링부터 임플란트까지 — 한화손보다이렉트 치아보험"&gt;
 &lt;meta property="og:description" content="미루기 쉬운 치과 치료비, 미리 준비해요. 보장과 보험료를 3분 만에 확인하고 카톡으로 공유하세요."&gt;
@@ -2703,103 +2772,55 @@
 &lt;meta property="og:url" content="https://m.hanwhadirect.com/ltr/dntl/"&gt;</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr"/>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="I32" s="12" t="inlineStr"/>
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>치아보험</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>한화손보다이렉트 직접</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/ltr/dntl/</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>모바일(m.)·PC(www) 메타 일치 + canonical</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- m./www 메타 상이·canonical 누락 가능 --&gt;</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>&lt;link rel="canonical" href="https://www.hanwhadirect.com/ltr/dntl/"&gt;
 &lt;link rel="alternate" media="only screen and (max-width: 640px)" href="https://m.hanwhadirect.com/ltr/dntl/"&gt;</t>
         </is>
       </c>
-      <c r="I32" s="12" t="inlineStr"/>
-      <c r="J32" s="12" t="inlineStr">
-        <is>
-          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>치아보험</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>한화손보다이렉트 직접</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/ltr/dntl/</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/dntl_cover.png"&gt;</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/dntl_cover.png" alt="치아보험 보장내용 안내"&gt;</t>
-        </is>
-      </c>
       <c r="I33" s="12" t="inlineStr"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
@@ -2810,52 +2831,48 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>운전자보험</t>
+          <t>치아보험</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>한화손보 캐롯</t>
+          <t>한화손보다이렉트</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>캐롯 분기</t>
+          <t>한화손보다이렉트 직접</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=driver</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
+          <t>https://m.hanwhadirect.com/ltr/dntl/</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
+          <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="자동차보험, 운전자보험, 해외여행보험 등 가입부터 관리까지 비대면으로 간편하게 가입. 한화손보…"&gt;</t>
+          <t>&lt;img src="/img/dntl_cover.png"&gt;</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="교통사고 벌금·변호사선임비·형사합의금까지. 한화손보 캐롯 운전자보험을 온라인에서 필요한 담보만 골라 설계하고 보험료를 확인하세요."&gt;</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>72자</t>
-        </is>
-      </c>
+          <t>&lt;img src="/img/dntl_cover.png" alt="치아보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>목적지: https://www.carrotins.com/long-term/driver</t>
+          <t>H1·alt·OG 원본은 실제 DOM 확인 후</t>
         </is>
       </c>
     </row>
@@ -2887,74 +2904,74 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="자동차보험, 운전자보험, 해외여행보험 등 가입부터 관리까지 비대면으로 간편하게 가입. 한화손보…"&gt;</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="교통사고 벌금·변호사선임비·형사합의금까지. 한화손보 캐롯 운전자보험을 온라인에서 필요한 담보만 골라 설계하고 보험료를 확인하세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>72자</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/long-term/driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>운전자보험</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=driver</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
           <t>분기(carrotBridge) 리다이렉트·canonical 정리</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- /cmcom/carrotBridge.do?carrot=driver : JS/meta refresh·302 금지 · canonical 없음 · campaignId 중복 --&gt;</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="H36" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- 서버 HTTP 301(Location)로 이동 + 목적지 canonical 통일 --&gt;
 &lt;link rel="canonical" href="https://www.carrotins.com/long-term/driver"&gt;
 &lt;!-- 또는 CM이 랭킹 확보시 hanwhadirect에 상품 콘텐츠 랜딩 신설 --&gt;</t>
         </is>
       </c>
-      <c r="I35" s="12" t="inlineStr"/>
-      <c r="J35" s="12" t="inlineStr">
-        <is>
-          <t>목적지: https://www.carrotins.com/long-term/driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>운전자보험</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>한화손보 캐롯</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>캐롯 분기</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=driver</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>&lt;title&gt; 교체</t>
-        </is>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;캐롯 운전자보험 무배당2604&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;한화손보 캐롯 운전자보험 | 벌금·변호사·합의금 보장&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>29자</t>
-        </is>
-      </c>
+      <c r="I36" s="12" t="inlineStr"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/long-term/driver</t>
@@ -2982,22 +2999,74 @@
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=driver</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>&lt;title&gt; 교체</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;캐롯 운전자보험 무배당2604&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보 캐롯 운전자보험 | 벌금·변호사·합의금 보장&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>29자</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/long-term/driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>운전자보험</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=driver</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H37" s="14" t="inlineStr">
+      <c r="H38" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="사고는 순간, 비용은 오래 간다 — 한화손보 캐롯 운전자보험"&gt;
 &lt;meta property="og:description" content="벌금·변호사비·합의금까지 대비하는 운전자보험. 3분 만에 담보를 골라 설계하고 카톡으로 공유해요."&gt;
@@ -3005,54 +3074,6 @@
 &lt;meta property="og:url" content="https://www.carrotins.com/long-term/driver"&gt;</t>
         </is>
       </c>
-      <c r="I37" s="12" t="inlineStr"/>
-      <c r="J37" s="12" t="inlineStr">
-        <is>
-          <t>목적지: https://www.carrotins.com/long-term/driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>운전자보험</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>한화손보 캐롯</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>캐롯 분기</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=driver</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
-        </is>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/driver_cover.png"&gt;</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/driver_cover.png" alt="운전자보험 보장내용 안내"&gt;</t>
-        </is>
-      </c>
       <c r="I38" s="12" t="inlineStr"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
@@ -3063,99 +3084,95 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
+          <t>운전자보험</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=driver</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>상품 이미지 alt 텍스트 보강</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/driver_cover.png"&gt;</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/driver_cover.png" alt="운전자보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr"/>
+      <c r="J39" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/long-term/driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
           <t>여성건강보험</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=woman</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>분기(carrotBridge) 리다이렉트·canonical 정리</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- /cmcom/carrotBridge.do?carrot=woman : JS/meta refresh·302 금지 · canonical 없음 · campaignId 중복 --&gt;</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr">
+      <c r="H40" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- 서버 HTTP 301(Location)로 이동 + 목적지 canonical 통일 --&gt;
 &lt;link rel="canonical" href="https://www.carrotins.com/long-term/women-signature/"&gt;
 &lt;!-- 또는 CM이 랭킹 확보시 hanwhadirect에 상품 콘텐츠 랜딩 신설 --&gt;</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr"/>
-      <c r="J39" s="12" t="inlineStr">
-        <is>
-          <t>목적지: https://www.carrotins.com/long-term/women-signature/</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>여성건강보험</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>한화손보 캐롯</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>캐롯 분기</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=woman</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>&lt;title&gt; 교체</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;한화 다이렉트 시그니처 여성 건강보험4.0(무)&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;한화손보 캐롯 여성건강보험 | 임신·출산·산후조리 지원&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>30자</t>
-        </is>
-      </c>
+      <c r="I40" s="12" t="inlineStr"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/long-term/women-signature/</t>
@@ -3183,29 +3200,29 @@
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=woman</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
+          <t>&lt;title&gt; 교체</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="아이가 생기고, 출산은 물론 산후조리원비용까지 지급해요. 임신지원금(1회한), 출산지원금(세부…"&gt;</t>
+          <t>&lt;title&gt;한화 다이렉트 시그니처 여성 건강보험4.0(무)&lt;/title&gt;</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="임신·출산지원금부터 산후조리원 비용까지. 한화손보 캐롯 시그니처 여성건강보험4.0의 여성 특화 보장을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
+          <t>&lt;title&gt;한화손보 캐롯 여성건강보험 | 임신·출산·산후조리 지원&lt;/title&gt;</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>79자</t>
+          <t>30자</t>
         </is>
       </c>
       <c r="J41" s="12" t="inlineStr">
@@ -3242,15 +3259,67 @@
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="아이가 생기고, 출산은 물론 산후조리원비용까지 지급해요. 임신지원금(1회한), 출산지원금(세부…"&gt;</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="임신·출산지원금부터 산후조리원 비용까지. 한화손보 캐롯 시그니처 여성건강보험4.0의 여성 특화 보장을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>79자</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/long-term/women-signature/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>여성건강보험</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=woman</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G42" s="14" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H42" s="14" t="inlineStr">
+      <c r="H43" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="임신부터 산후조리까지, 여성을 위한 설계 — 한화손보 캐롯"&gt;
 &lt;meta property="og:description" content="출산지원금과 산후조리원 비용까지 챙기는 여성건강보험. 3분 만에 설계하고 카톡으로 공유해요."&gt;
@@ -3258,54 +3327,6 @@
 &lt;meta property="og:url" content="https://www.carrotins.com/long-term/women-signature/"&gt;</t>
         </is>
       </c>
-      <c r="I42" s="12" t="inlineStr"/>
-      <c r="J42" s="12" t="inlineStr">
-        <is>
-          <t>목적지: https://www.carrotins.com/long-term/women-signature/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>여성건강보험</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>한화손보 캐롯</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>캐롯 분기</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=woman</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/woman_cover.png"&gt;</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/woman_cover.png" alt="여성건강보험 보장내용 안내"&gt;</t>
-        </is>
-      </c>
       <c r="I43" s="12" t="inlineStr"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
@@ -3316,7 +3337,7 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>임신·출산(태아)보험</t>
+          <t>여성건강보험</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -3331,37 +3352,33 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=birth</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=woman</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>&lt;title&gt; 교체</t>
+          <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;(전용 색인 노출 약함 — 태아보험 SERP를 경쟁사가 점유)&lt;/title&gt;</t>
+          <t>&lt;img src="/img/woman_cover.png"&gt;</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>&lt;title&gt;한화손보 캐롯 태아보험 | 임신·출산·선천이상 보장&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>28자</t>
-        </is>
-      </c>
+          <t>&lt;img src="/img/woman_cover.png" alt="여성건강보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>목적지: https://www.carrotins.com/</t>
+          <t>목적지: https://www.carrotins.com/long-term/women-signature/</t>
         </is>
       </c>
     </row>
@@ -3393,22 +3410,22 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
+          <t>&lt;title&gt; 교체</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+          <t>&lt;title&gt;(전용 색인 노출 약함 — 태아보험 SERP를 경쟁사가 점유)&lt;/title&gt;</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="임신 중 가입부터 미숙아·선천이상 수술·입원 보장까지. 한화손보 캐롯 태아보험을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
+          <t>&lt;title&gt;한화손보 캐롯 태아보험 | 임신·출산·선천이상 보장&lt;/title&gt;</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>67자</t>
+          <t>28자</t>
         </is>
       </c>
       <c r="J45" s="12" t="inlineStr">
@@ -3445,65 +3462,117 @@
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>&lt;!-- description 미설정/부적절 → 본문·폼 텍스트가 스니펫으로 노출 --&gt;</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="임신 중 가입부터 미숙아·선천이상 수술·입원 보장까지. 한화손보 캐롯 태아보험을 온라인에서 설계하고 보험료를 확인하세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>67자</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>임신·출산(태아)보험</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=birth</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
           <t>분기(carrotBridge) 리다이렉트·canonical 정리</t>
         </is>
       </c>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- /cmcom/carrotBridge.do?carrot=birth : JS/meta refresh·302 금지 · canonical 없음 · campaignId 중복 --&gt;</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr">
+      <c r="H47" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- 서버 HTTP 301(Location)로 이동 + 목적지 canonical 통일 --&gt;
 &lt;link rel="canonical" href="https://www.carrotins.com/"&gt;
 &lt;!-- 또는 CM이 랭킹 확보시 hanwhadirect에 상품 콘텐츠 랜딩 신설 --&gt;</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr"/>
-      <c r="J46" s="12" t="inlineStr">
+      <c r="I47" s="12" t="inlineStr"/>
+      <c r="J47" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>임신·출산(태아)보험</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>한화손보 캐롯</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>캐롯 분기</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=birth</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G47" s="14" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H47" s="14" t="inlineStr">
+      <c r="H48" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="엄마가 되기 전에, 태아보험부터 — 한화손보 캐롯"&gt;
 &lt;meta property="og:description" content="임신 22주 전 가입·태아 특약까지. 3분 만에 설계하고 카톡으로 공유해요."&gt;
@@ -3511,54 +3580,6 @@
 &lt;meta property="og:url" content="https://www.carrotins.com/"&gt;</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr"/>
-      <c r="J47" s="12" t="inlineStr">
-        <is>
-          <t>목적지: https://www.carrotins.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>임신·출산(태아)보험</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>한화손보 캐롯</t>
-        </is>
-      </c>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>캐롯 분기</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=birth</t>
-        </is>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/birth_cover.png"&gt;</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/birth_cover.png" alt="임신·출산(태아)보험 보장내용 안내"&gt;</t>
-        </is>
-      </c>
       <c r="I48" s="12" t="inlineStr"/>
       <c r="J48" s="12" t="inlineStr">
         <is>
@@ -3569,7 +3590,7 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>해외여행보험</t>
+          <t>임신·출산(태아)보험</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
@@ -3584,37 +3605,33 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=birth</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
+          <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="출국 7일 이전 가입 ; 2명 이상 함께 가입 ; 10% 환급 ; 고객님께 안내드립니다. 전쟁…"&gt;</t>
+          <t>&lt;img src="/img/birth_cover.png"&gt;</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="출국 전 간편 가입과 무사고 시 캐시백까지. 한화손보 캐롯 해외여행보험을 개인정보 없이 온라인에서 비교하고 보험료를 확인하세요."&gt;</t>
-        </is>
-      </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>71자</t>
-        </is>
-      </c>
+          <t>&lt;img src="/img/birth_cover.png" alt="임신·출산(태아)보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr"/>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>목적지: https://www.carrotins.com/product/overseas</t>
+          <t>목적지: https://www.carrotins.com/</t>
         </is>
       </c>
     </row>
@@ -3646,74 +3663,74 @@
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="출국 7일 이전 가입 ; 2명 이상 함께 가입 ; 10% 환급 ; 고객님께 안내드립니다. 전쟁…"&gt;</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="출국 전 간편 가입과 무사고 시 캐시백까지. 한화손보 캐롯 해외여행보험을 개인정보 없이 온라인에서 비교하고 보험료를 확인하세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>71자</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/product/overseas</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>해외여행보험</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
           <t>분기(carrotBridge) 리다이렉트·canonical 정리</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="G51" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- /cmcom/carrotBridge.do?carrot=overseas : JS/meta refresh·302 금지 · canonical 없음 · campaignId 중복 --&gt;</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr">
+      <c r="H51" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- 서버 HTTP 301(Location)로 이동 + 목적지 canonical 통일 --&gt;
 &lt;link rel="canonical" href="https://www.carrotins.com/product/overseas"&gt;
 &lt;!-- 또는 CM이 랭킹 확보시 hanwhadirect에 상품 콘텐츠 랜딩 신설 --&gt;</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr"/>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>목적지: https://www.carrotins.com/product/overseas</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>해외여행보험</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>한화손보 캐롯</t>
-        </is>
-      </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>캐롯 분기</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas</t>
-        </is>
-      </c>
-      <c r="E51" s="15" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>&lt;title&gt; 교체</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;한화손보 캐롯 해외여행보험 | 여행자 보험료 개인정보 없이 간편 확인&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;한화손보 캐롯 해외여행보험 | 개인정보 없이 보험료 확인&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>31자</t>
-        </is>
-      </c>
+      <c r="I51" s="12" t="inlineStr"/>
       <c r="J51" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/product/overseas</t>
@@ -3741,22 +3758,74 @@
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas</t>
         </is>
       </c>
-      <c r="E52" s="16" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>&lt;title&gt; 교체</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보 캐롯 해외여행보험 | 여행자 보험료 개인정보 없이 간편 확인&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보 캐롯 해외여행보험 | 개인정보 없이 보험료 확인&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>31자</t>
+        </is>
+      </c>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/product/overseas</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>해외여행보험</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G52" s="14" t="inlineStr">
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H52" s="14" t="inlineStr">
+      <c r="H53" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="여행 전 3분, 한화손보 캐롯 해외여행보험"&gt;
 &lt;meta property="og:description" content="출국 전 간편가입·무사고 캐시백. 개인정보 없이 보험료를 바로 확인해요."&gt;
@@ -3764,54 +3833,6 @@
 &lt;meta property="og:url" content="https://www.carrotins.com/product/overseas"&gt;</t>
         </is>
       </c>
-      <c r="I52" s="12" t="inlineStr"/>
-      <c r="J52" s="12" t="inlineStr">
-        <is>
-          <t>목적지: https://www.carrotins.com/product/overseas</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>해외여행보험</t>
-        </is>
-      </c>
-      <c r="B53" s="12" t="inlineStr">
-        <is>
-          <t>한화손보 캐롯</t>
-        </is>
-      </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>캐롯 분기</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas</t>
-        </is>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="F53" s="12" t="inlineStr">
-        <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/overseas_cover.png"&gt;</t>
-        </is>
-      </c>
-      <c r="H53" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/overseas_cover.png" alt="해외여행보험 보장내용 안내"&gt;</t>
-        </is>
-      </c>
       <c r="I53" s="12" t="inlineStr"/>
       <c r="J53" s="12" t="inlineStr">
         <is>
@@ -3822,7 +3843,7 @@
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>해외장기체류보험</t>
+          <t>해외여행보험</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
@@ -3837,37 +3858,33 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>상</t>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>&lt;meta name="description"&gt; 신설/교체</t>
+          <t>상품 이미지 alt 텍스트 보강</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="해외체류 중 질병이나 상해를 입어 해외의료기관에서 치료를 받은 경우 최대 10만달러까지 보장해…"&gt;</t>
+          <t>&lt;img src="/img/overseas_cover.png"&gt;</t>
         </is>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>&lt;meta name="description" content="3개월 초과 해외체류·유학 중 질병·상해 의료비를 최대 10만달러까지. 한화손보 캐롯 해외장기체류보험을 온라인에서 확인하세요."&gt;</t>
-        </is>
-      </c>
-      <c r="I54" s="12" t="inlineStr">
-        <is>
-          <t>70자</t>
-        </is>
-      </c>
+          <t>&lt;img src="/img/overseas_cover.png" alt="해외여행보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr"/>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
+          <t>목적지: https://www.carrotins.com/product/overseas</t>
         </is>
       </c>
     </row>
@@ -3899,74 +3916,74 @@
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
+          <t>&lt;meta name="description"&gt; 신설/교체</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="해외체류 중 질병이나 상해를 입어 해외의료기관에서 치료를 받은 경우 최대 10만달러까지 보장해…"&gt;</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>&lt;meta name="description" content="3개월 초과 해외체류·유학 중 질병·상해 의료비를 최대 10만달러까지. 한화손보 캐롯 해외장기체류보험을 온라인에서 확인하세요."&gt;</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>70자</t>
+        </is>
+      </c>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>해외장기체류보험</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
           <t>분기(carrotBridge) 리다이렉트·canonical 정리</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
+      <c r="G56" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- /cmcom/carrotBridge.do?carrot=overseas-long : JS/meta refresh·302 금지 · canonical 없음 · campaignId 중복 --&gt;</t>
         </is>
       </c>
-      <c r="H55" s="14" t="inlineStr">
+      <c r="H56" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- 서버 HTTP 301(Location)로 이동 + 목적지 canonical 통일 --&gt;
 &lt;link rel="canonical" href="https://www.carrotins.com/product/overseas-long/intro"&gt;
 &lt;!-- 또는 CM이 랭킹 확보시 hanwhadirect에 상품 콘텐츠 랜딩 신설 --&gt;</t>
         </is>
       </c>
-      <c r="I55" s="12" t="inlineStr"/>
-      <c r="J55" s="12" t="inlineStr">
-        <is>
-          <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>해외장기체류보험</t>
-        </is>
-      </c>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>한화손보 캐롯</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>캐롯 분기</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
-        </is>
-      </c>
-      <c r="E56" s="15" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>&lt;title&gt; 교체</t>
-        </is>
-      </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;한화손보 캐롯 해외장기체류보험 | 3개월 초과 여행, 장기 유학시 보장&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="H56" s="14" t="inlineStr">
-        <is>
-          <t>&lt;title&gt;한화손보 캐롯 해외장기체류보험 | 유학·장기체류 보장&lt;/title&gt;</t>
-        </is>
-      </c>
-      <c r="I56" s="12" t="inlineStr">
-        <is>
-          <t>29자</t>
-        </is>
-      </c>
+      <c r="I56" s="12" t="inlineStr"/>
       <c r="J56" s="12" t="inlineStr">
         <is>
           <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
@@ -3994,22 +4011,74 @@
           <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
         </is>
       </c>
-      <c r="E57" s="16" t="inlineStr">
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>&lt;title&gt; 교체</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보 캐롯 해외장기체류보험 | 3개월 초과 여행, 장기 유학시 보장&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>&lt;title&gt;한화손보 캐롯 해외장기체류보험 | 유학·장기체류 보장&lt;/title&gt;</t>
+        </is>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>29자</t>
+        </is>
+      </c>
+      <c r="J57" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>해외장기체류보험</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>OG 태그 세트 추가/점검</t>
         </is>
       </c>
-      <c r="G57" s="14" t="inlineStr">
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>&lt;!-- og:* 태그 없음/부분 --&gt;</t>
         </is>
       </c>
-      <c r="H57" s="14" t="inlineStr">
+      <c r="H58" s="14" t="inlineStr">
         <is>
           <t>&lt;meta property="og:title" content="유학·장기출장 전 필수 — 한화손보 캐롯 해외장기체류보험"&gt;
 &lt;meta property="og:description" content="3개월 넘는 해외체류, 현지 의료비까지 대비하는 장기체류보험. 개인정보 없이 보험료를 확인해요."&gt;
@@ -4017,54 +4086,6 @@
 &lt;meta property="og:url" content="https://www.carrotins.com/product/overseas-long/intro"&gt;</t>
         </is>
       </c>
-      <c r="I57" s="12" t="inlineStr"/>
-      <c r="J57" s="12" t="inlineStr">
-        <is>
-          <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>해외장기체류보험</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>한화손보 캐롯</t>
-        </is>
-      </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>캐롯 분기</t>
-        </is>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
-        </is>
-      </c>
-      <c r="E58" s="16" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>상품 이미지 alt 텍스트 보강</t>
-        </is>
-      </c>
-      <c r="G58" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/overseaslong_cover.png"&gt;</t>
-        </is>
-      </c>
-      <c r="H58" s="14" t="inlineStr">
-        <is>
-          <t>&lt;img src="/img/overseaslong_cover.png" alt="해외장기체류보험 보장내용 안내"&gt;</t>
-        </is>
-      </c>
       <c r="I58" s="12" t="inlineStr"/>
       <c r="J58" s="12" t="inlineStr">
         <is>
@@ -4072,8 +4093,56 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>해외장기체류보험</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>한화손보 캐롯</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>캐롯 분기</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>https://m.hanwhadirect.com/cmcom/carrotBridge.do?carrot=overseas-long</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>상품 이미지 alt 텍스트 보강</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/overseaslong_cover.png"&gt;</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="/img/overseaslong_cover.png" alt="해외장기체류보험 보장내용 안내"&gt;</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="inlineStr"/>
+      <c r="J59" s="12" t="inlineStr">
+        <is>
+          <t>목적지: https://www.carrotins.com/product/overseas-long/intro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J58"/>
+  <autoFilter ref="A1:J59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4466,4 +4535,268 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>피해야 할 것</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>예시(잘못)</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>예시(권장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Redirect</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>JS·meta refresh 이동</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>location.href / &lt;meta http-equiv=refresh&gt;</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>서버 HTTP 301/3xx</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>HTTP 301 Location 헤더</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Canonical URL</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>파라미터로 중복 URL</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>?event=code01 · ?event=none</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>대표 URL 1개 지정</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>&lt;link rel="canonical" href="…"&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Meta Tag</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>title·description·og 누락</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>(태그 없음)</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>문서 메타 제공</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>title · description · og</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>태그 위치</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>head 전용 태그가 body에</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>&lt;body&gt;&lt;title&gt;…</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>head 안에 위치</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>&lt;head&gt;&lt;title&gt;…&lt;/title&gt;&lt;/head&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Link Syntax</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>JS 링크(onclick)</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>&lt;a href="#" onclick="goto()"&gt;</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>일반 &lt;a href&gt; 링크</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>&lt;a href="/ltr/cncr/"&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Frame Tag</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>frame로 콘텐츠 구성</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>&lt;frame src="…"&gt;</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>일반 HTML 마크업</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>&lt;main&gt;·&lt;section&gt; 구조</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>앵커 텍스트</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>‘여기 클릭’ 등 모호</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>&lt;a&gt;여기&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>대표 키워드로 간결</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>&lt;a&gt;암보험 보장내용&lt;/a&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>이미지 alt</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>alt 속성 누락</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img src="…"&gt;</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>대체 텍스트 필수</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>&lt;img alt="…보장내용"&gt;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>